--- a/outputs/butter/silpo/primary_chain_output.xlsx
+++ b/outputs/butter/silpo/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08225840900715364</v>
+        <v>0.08225840900720094</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>2.681802621264837e-12</v>
+        <v>2.681802621266499e-12</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.300695796395212e-20</v>
+        <v>1.300695796394998e-20</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05640422694264773</v>
+        <v>0.05640422694264767</v>
       </c>
       <c r="C3" t="n">
         <v>0.01</v>
@@ -580,7 +580,7 @@
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.926918418202639e-13</v>
+        <v>1.926918418201579e-13</v>
       </c>
       <c r="G3" t="n">
         <v>0.1</v>
@@ -630,7 +630,7 @@
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>8.70860721185971e-05</v>
+        <v>8.708607211858895e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.04166666666666662</v>
@@ -942,22 +942,22 @@
         <v>218</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2127764229425361</v>
+        <v>-0.2127764229425364</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2740532058530188</v>
+        <v>0.2740532058530208</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8083252331134957</v>
+        <v>-0.8083252331134949</v>
       </c>
       <c r="M2" t="n">
-        <v>1.252374581737896e-26</v>
+        <v>1.252374581588286e-26</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7873814868471209</v>
+        <v>0.787381486847105</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2011263550434567</v>
+        <v>0.2011263550434396</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
@@ -1024,10 +1024,10 @@
         <v>41</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2001943602714764</v>
+        <v>0.2001943602714746</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4257756633486405</v>
+        <v>-0.4257756633486562</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -1098,22 +1098,22 @@
         <v>39</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04860976737983126</v>
+        <v>0.04860976737983232</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1264841571269478</v>
+        <v>-0.1264841571269484</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8756967529857956</v>
+        <v>-0.8756967529857952</v>
       </c>
       <c r="M4" t="n">
-        <v>2.214481682557665e-08</v>
+        <v>2.214481682565935e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5941357916590037</v>
+        <v>0.5941357916588494</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5501601441288803</v>
+        <v>0.5501601441286696</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3043740439991276</v>
+        <v>0.3043740439991278</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5287391650637272</v>
+        <v>0.5287391650637225</v>
       </c>
       <c r="G2" t="n">
         <v>4.220381385301966e-84</v>
@@ -1247,13 +1247,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.01144894530681835</v>
+        <v>0.01144894530682034</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09344174279103216</v>
+        <v>0.09344174279046094</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6443904339549587</v>
+        <v>0.6443904339547601</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5591712653384464</v>
+        <v>0.559171265338444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04666547489468428</v>
+        <v>0.04666547489468913</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8050949849331446</v>
+        <v>0.8050949849331526</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -57363,10 +57363,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.5437076425441756</v>
+        <v>-0.5437076425441754</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3309312196016395</v>
+        <v>-0.330931219601639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -57379,10 +57379,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.4804346363943778</v>
+        <v>-0.4804346363943776</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2924196897746271</v>
+        <v>-0.2924196897746266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57395,10 +57395,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4877979195156134</v>
+        <v>-0.4877979195156132</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2969014002986514</v>
+        <v>-0.2969014002986509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57411,10 +57411,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.4869410305889973</v>
+        <v>-0.4869410305889971</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2963798492381931</v>
+        <v>-0.2963798492381926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57427,10 +57427,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.4870407495079181</v>
+        <v>-0.4870407495079179</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2964405438116616</v>
+        <v>-0.2964405438116611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57443,10 +57443,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.4870291448967697</v>
+        <v>-0.4870291448967695</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2964334805890401</v>
+        <v>-0.2964334805890396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57459,10 +57459,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.4870304953626729</v>
+        <v>-0.4870304953626727</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2964343025589618</v>
+        <v>-0.2964343025589613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57475,10 +57475,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4870303382046146</v>
+        <v>-0.4870303382046144</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2964342069036797</v>
+        <v>-0.2964342069036792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57491,10 +57491,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.487030356493603</v>
+        <v>-0.4870303564936028</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2964342180353924</v>
+        <v>-0.2964342180353919</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57507,10 +57507,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.4870303543652547</v>
+        <v>-0.4870303543652544</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2964342167399592</v>
+        <v>-0.2964342167399587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57523,10 +57523,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.4870303546129374</v>
+        <v>-0.4870303546129372</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2964342168907129</v>
+        <v>-0.2964342168907124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57539,10 +57539,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4870303545841138</v>
+        <v>-0.4870303545841136</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2964342168731692</v>
+        <v>-0.2964342168731687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57555,10 +57555,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.4870303545874681</v>
+        <v>-0.4870303545874679</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2964342168752108</v>
+        <v>-0.2964342168752103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57571,10 +57571,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4870303545870777</v>
+        <v>-0.4870303545870775</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2964342168749732</v>
+        <v>-0.2964342168749727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57587,10 +57587,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.4870303545871231</v>
+        <v>-0.487030354587123</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.2964342168750009</v>
+        <v>-0.2964342168750004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57603,10 +57603,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.4870303545871179</v>
+        <v>-0.4870303545871176</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.2964342168749977</v>
+        <v>-0.2964342168749972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57619,10 +57619,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.4870303545871185</v>
+        <v>-0.4870303545871183</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57635,10 +57635,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.4870303545871184</v>
+        <v>-0.4870303545871182</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57651,10 +57651,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.4870303545871184</v>
+        <v>-0.4870303545871182</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57667,10 +57667,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.4870303545871184</v>
+        <v>-0.4870303545871182</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57683,10 +57683,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.4870303545871184</v>
+        <v>-0.4870303545871182</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -57699,10 +57699,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>0.06009522591878209</v>
+        <v>0.06009522591878243</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01148545853895083</v>
+        <v>0.01148545853895011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -57715,10 +57715,10 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.06495635205286496</v>
+        <v>0.06495635205286528</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01241452173510348</v>
+        <v>0.01241452173510269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -57731,10 +57731,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>0.06534957043136644</v>
+        <v>0.06534957043136674</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01248967401740184</v>
+        <v>0.01248967401740104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -57747,10 +57747,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06538137801852351</v>
+        <v>0.06538137801852381</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01249575311466674</v>
+        <v>0.01249575311466595</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -57763,10 +57763,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>0.06538395094658604</v>
+        <v>0.06538395094658635</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01249624485520244</v>
+        <v>0.01249624485520164</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -57779,10 +57779,10 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>0.065384159071735</v>
+        <v>0.06538415907173531</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01249628463228511</v>
+        <v>0.01249628463228431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -57795,10 +57795,10 @@
         <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>0.06538417590705903</v>
+        <v>0.06538417590705933</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01249628784986875</v>
+        <v>0.01249628784986795</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -57811,10 +57811,10 @@
         <v>7</v>
       </c>
       <c r="B30" t="n">
-        <v>0.06538417726887492</v>
+        <v>0.06538417726887523</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01249628811014034</v>
+        <v>0.01249628811013954</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -57827,10 +57827,10 @@
         <v>8</v>
       </c>
       <c r="B31" t="n">
-        <v>0.06538417737903274</v>
+        <v>0.06538417737903304</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01249628813119381</v>
+        <v>0.01249628813119301</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -57843,10 +57843,10 @@
         <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>0.06538417738794344</v>
+        <v>0.06538417738794375</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01249628813289683</v>
+        <v>0.01249628813289604</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -57859,10 +57859,10 @@
         <v>10</v>
       </c>
       <c r="B33" t="n">
-        <v>0.06538417738866423</v>
+        <v>0.06538417738866455</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01249628813303459</v>
+        <v>0.01249628813303379</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -57875,10 +57875,10 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>0.06538417738872254</v>
+        <v>0.06538417738872285</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01249628813304574</v>
+        <v>0.01249628813304494</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -57891,10 +57891,10 @@
         <v>12</v>
       </c>
       <c r="B35" t="n">
-        <v>0.06538417738872726</v>
+        <v>0.06538417738872757</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01249628813304664</v>
+        <v>0.01249628813304584</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -57907,10 +57907,10 @@
         <v>13</v>
       </c>
       <c r="B36" t="n">
-        <v>0.06538417738872764</v>
+        <v>0.06538417738872794</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01249628813304671</v>
+        <v>0.01249628813304591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -57923,10 +57923,10 @@
         <v>14</v>
       </c>
       <c r="B37" t="n">
-        <v>0.06538417738872766</v>
+        <v>0.06538417738872797</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01249628813304672</v>
+        <v>0.01249628813304592</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -57939,10 +57939,10 @@
         <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>0.06538417738872768</v>
+        <v>0.06538417738872798</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01249628813304672</v>
+        <v>0.01249628813304592</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -57955,10 +57955,10 @@
         <v>16</v>
       </c>
       <c r="B39" t="n">
-        <v>0.06538417738872768</v>
+        <v>0.06538417738872798</v>
       </c>
       <c r="C39" t="n">
-        <v>0.01249628813304672</v>
+        <v>0.01249628813304592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -57971,10 +57971,10 @@
         <v>17</v>
       </c>
       <c r="B40" t="n">
-        <v>0.06538417738872768</v>
+        <v>0.06538417738872798</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01249628813304672</v>
+        <v>0.01249628813304592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -57987,10 +57987,10 @@
         <v>18</v>
       </c>
       <c r="B41" t="n">
-        <v>0.06538417738872768</v>
+        <v>0.06538417738872798</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01249628813304672</v>
+        <v>0.01249628813304592</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -58003,10 +58003,10 @@
         <v>19</v>
       </c>
       <c r="B42" t="n">
-        <v>0.06538417738872768</v>
+        <v>0.06538417738872798</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01249628813304672</v>
+        <v>0.01249628813304592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -58019,10 +58019,10 @@
         <v>20</v>
       </c>
       <c r="B43" t="n">
-        <v>0.06538417738872768</v>
+        <v>0.06538417738872798</v>
       </c>
       <c r="C43" t="n">
-        <v>0.01249628813304672</v>
+        <v>0.01249628813304592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
